--- a/data/merged_user_info.xlsx
+++ b/data/merged_user_info.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\Output\user_info_merging\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88AC05C-DD25-475E-A5BF-5FB92B137B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C93BCD6-22B6-41CE-BE39-ACB546F167B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -794,6 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AN17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1063,7 +1064,7 @@
       </c>
       <c r="AL2" s="2">
         <f ca="1">INT(TODAY() - DATEVALUE(B2))</f>
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="AM2">
         <f>YEAR(B2)</f>
@@ -1169,15 +1170,15 @@
         <v>56</v>
       </c>
       <c r="AL3" s="2">
-        <f t="shared" ref="AL3:AL17" ca="1" si="0">INT(TODAY() - DATEVALUE(B3))</f>
-        <v>917</v>
+        <f ca="1">INT(TODAY() - DATEVALUE(B3))</f>
+        <v>918</v>
       </c>
       <c r="AM3">
-        <f t="shared" ref="AM3:AM17" si="1">YEAR(B3)</f>
+        <f t="shared" ref="AM3:AM17" si="0">YEAR(B3)</f>
         <v>2024</v>
       </c>
       <c r="AN3">
-        <f t="shared" ref="AN3:AN17" si="2">MONTH(B3)</f>
+        <f t="shared" ref="AN3:AN17" si="1">MONTH(B3)</f>
         <v>3</v>
       </c>
     </row>
@@ -1276,15 +1277,15 @@
         <v>63</v>
       </c>
       <c r="AL4" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <f ca="1">INT(TODAY() - DATEVALUE(B4))</f>
+        <v>68</v>
       </c>
       <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN4">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN4">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1392,15 +1393,15 @@
         <v>71</v>
       </c>
       <c r="AL5" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <f t="shared" ref="AL3:AL17" ca="1" si="2">INT(TODAY() - DATEVALUE(B5))</f>
+        <v>63</v>
       </c>
       <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN5">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN5">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1505,15 +1506,15 @@
         <v>78</v>
       </c>
       <c r="AL6" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>57</v>
       </c>
       <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN6">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN6">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1606,15 +1607,15 @@
         <v>82</v>
       </c>
       <c r="AL7" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>55</v>
       </c>
       <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN7">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN7">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1722,15 +1723,15 @@
         <v>88</v>
       </c>
       <c r="AL8" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>54</v>
       </c>
       <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN8">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN8">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -1829,15 +1830,15 @@
         <v>93</v>
       </c>
       <c r="AL9" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>34</v>
       </c>
       <c r="AM9">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN9">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN9">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -1942,15 +1943,15 @@
         <v>100</v>
       </c>
       <c r="AL10" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>30</v>
       </c>
       <c r="AM10">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN10">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN10">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -2055,15 +2056,15 @@
         <v>106</v>
       </c>
       <c r="AL11" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>29</v>
       </c>
       <c r="AM11">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN11">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN11">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -2162,15 +2163,15 @@
         <v>111</v>
       </c>
       <c r="AL12" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>22</v>
       </c>
       <c r="AM12">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN12">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN12">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -2269,15 +2270,15 @@
         <v>116</v>
       </c>
       <c r="AL13" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>21</v>
       </c>
       <c r="AM13">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN13">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN13">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -2367,15 +2368,15 @@
         <v>120</v>
       </c>
       <c r="AL14" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>21</v>
       </c>
       <c r="AM14">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN14">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN14">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -2474,15 +2475,15 @@
         <v>124</v>
       </c>
       <c r="AL15" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>20</v>
       </c>
       <c r="AM15">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN15">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN15">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -2587,15 +2588,15 @@
         <v>130</v>
       </c>
       <c r="AL16" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>19</v>
       </c>
       <c r="AM16">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN16">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN16">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
@@ -2694,15 +2695,15 @@
         <v>134</v>
       </c>
       <c r="AL17" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>18</v>
       </c>
       <c r="AM17">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="AN17">
         <f t="shared" si="1"/>
-        <v>2026</v>
-      </c>
-      <c r="AN17">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
